--- a/docs/api-spec/PAEON_API_명세서.xlsx
+++ b/docs/api-spec/PAEON_API_명세서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도메인별 비고" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API 명세서'!$A$1:$F$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API 명세서'!$A$1:$F$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1184,22 +1184,22 @@
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>이용 적합성</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/health/schemas/active</t>
+          <t>/eligibility/assessments/{assessment_id}/acknowledge-emergency</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>현재 사용중인 입력 스키마 조회</t>
+          <t>응급 안내 확인 후 계속 진행(v5 신규)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>schema_version, model_scope</t>
+          <t>→ emergency_acknowledged_at 기록</t>
         </is>
       </c>
     </row>
@@ -1221,17 +1221,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/health/records</t>
+          <t>/health/schemas/active</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>건강기록 신규 생성</t>
+          <t>현재 사용중인 입력 스키마 조회</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>health_schema_id, input_type(initial/interim_reassessment/full_reassessment/weekly_bp/manual), examination_date, alcohol_frequency(필수로 변경)</t>
+          <t>schema_version, model_scope</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/health/records/{id}/measurements</t>
+          <t>/health/records</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>측정값 일괄 등록</t>
+          <t>건강기록 신규 생성</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>metric_code, value_num, unit, measured_on</t>
+          <t>health_schema_id, input_type(initial/interim_reassessment/full_reassessment/weekly_bp/manual), examination_date, alcohol_frequency(필수로 변경)</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1285,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/health/records/{id}</t>
+          <t>/health/records/{id}/measurements</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>건강기록 상세 (측정값+검증오류 포함)</t>
+          <t>측정값 일괄 등록</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>health_measurements[], health_validation_errors[]</t>
+          <t>metric_code, value_num, unit, measured_on</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>/health/records</t>
+          <t>/health/records/{id}</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>건강기록 이력 목록</t>
+          <t>건강기록 상세 (측정값+검증오류 포함)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>examination_date, verified_at</t>
+          <t>health_measurements[], health_validation_errors[]</t>
         </is>
       </c>
     </row>
@@ -1349,17 +1349,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>/health/files</t>
+          <t>/health/records</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>검진결과지 업로드</t>
+          <t>건강기록 이력 목록</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>file_purpose, storage_object_key → file_job_id</t>
+          <t>examination_date, verified_at</t>
         </is>
       </c>
     </row>
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/health/files/{file_job_id}</t>
+          <t>/health/files</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>업로드·OCR 처리 상태 조회</t>
+          <t>검진결과지 업로드</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>status, ocr_extraction_results[]</t>
+          <t>file_purpose, storage_object_key → file_job_id</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>/health/files/{file_job_id}/ocr-results/{extraction_result_id}/accept</t>
+          <t>/health/files/{file_job_id}</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>OCR 추출값 확정 반영</t>
+          <t>업로드·OCR 처리 상태 조회</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1433,29 +1433,29 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>accepted_by_user=true → health_measurements 반영</t>
+          <t>status, ocr_extraction_results[]</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>설문</t>
+          <t>건강정보 입력</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>/surveys/{survey_type}/active</t>
+          <t>/health/files/{file_job_id}/ocr-results/{extraction_result_id}/accept</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>활성 설문 버전+문항+옵션 조회</t>
+          <t>OCR 추출값 확정 반영</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>survey_version_id, survey_questions[], survey_options[]</t>
+          <t>accepted_by_user=true → health_measurements 반영</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1477,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances</t>
+          <t>/surveys/{survey_type}/active</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>설문 응답 세션 시작</t>
+          <t>활성 설문 버전+문항+옵션 조회</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>survey_version_id, health_record_id → survey_instance_id</t>
+          <t>survey_version_id, survey_questions[], survey_options[]</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}/responses</t>
+          <t>/survey-instances</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>문항 응답 저장(배치)</t>
+          <t>설문 응답 세션 시작</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>question_id, option_ids[](단일 1개/복수 N개), answer_json</t>
+          <t>survey_version_id, health_record_id → survey_instance_id</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}/submit</t>
+          <t>/survey-instances/{id}/responses</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>설문 제출 확정</t>
+          <t>문항 응답 저장(배치)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>submitted_at 기록</t>
+          <t>question_id, option_ids[](단일 1개/복수 N개), answer_json</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1573,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}</t>
+          <t>/survey-instances/{id}/submit</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>응답 현황 조회</t>
+          <t>설문 제출 확정</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1593,29 +1593,29 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>status, survey_responses[]</t>
+          <t>submitted_at 기록</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>예측 실행·결과</t>
+          <t>설문</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>/predictions/jobs</t>
+          <t>/survey-instances/{id}</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>예측 실행 요청(비동기)</t>
+          <t>응답 현황 조회</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>health_record_id, request_type(auto/manual) → job_id, status</t>
+          <t>status, survey_responses[]</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>/predictions/jobs/{job_id}</t>
+          <t>/predictions/jobs</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>작업 상태 조회(폴링)</t>
+          <t>예측 실행 요청(비동기)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>status, prediction_job_runs[]</t>
+          <t>health_record_id, request_type(auto/manual) → job_id, status</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>/predictions/{prediction_id}</t>
+          <t>/predictions/jobs/{job_id}</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>예측 결과 상세</t>
+          <t>작업 상태 조회(폴링)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>risk_level, score, vascular_age, prediction_factors[]</t>
+          <t>status, prediction_job_runs[]</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1706,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>/predictions/latest</t>
+          <t>/predictions/{prediction_id}</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>최신 예측 결과 조회</t>
+          <t>예측 결과 상세</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>prediction_id, predicted_at</t>
+          <t>risk_level, score, vascular_age, prediction_factors[]</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>/predictions</t>
+          <t>/predictions/latest</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>예측 이력 목록(추이)</t>
+          <t>최신 예측 결과 조회</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>score, vascular_age, predicted_at[]</t>
+          <t>prediction_id, predicted_at</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>/predictions/{prediction_id}/disclosures</t>
+          <t>/predictions</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>안전 고지 문구 조회</t>
+          <t>예측 이력 목록(추이)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1785,14 +1785,14 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>disclosure_type, message_version</t>
+          <t>score, vascular_age, predicted_at[]</t>
         </is>
       </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>예측 실행·결과</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>/admin/models</t>
+          <t>/predictions/{prediction_id}/disclosures</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>질환별 모델 목록</t>
+          <t>안전 고지 문구 조회</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>disease_id, model_code, prediction_scope</t>
+          <t>disclosure_type, message_version</t>
         </is>
       </c>
     </row>
@@ -1829,17 +1829,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/{model_id}/versions</t>
+          <t>/admin/models</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>신규 모델 버전 등록</t>
+          <t>질환별 모델 목록 — v5: MODEL_A만 운영(모델B 삭제)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>artifact_uri, preprocessing_version, threshold_config</t>
+          <t>disease_id, model_code, prediction_scope</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/activate</t>
+          <t>/admin/models/{model_id}/versions</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>버전 활성화</t>
+          <t>신규 모델 버전 등록</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>released_at 기록, 기존 버전 retired_at</t>
+          <t>artifact_uri, preprocessing_version, threshold_config</t>
         </is>
       </c>
     </row>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/feature-contracts</t>
+          <t>/admin/models/versions/{version_id}/activate</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>피처 계약 조회</t>
+          <t>버전 활성화</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>feature_definition_id, required, missing_value_policy</t>
+          <t>released_at 기록, 기존 버전 retired_at</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>/admin/training-datasets</t>
+          <t>/admin/models/versions/{version_id}/feature-contracts</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>학습 데이터셋 등록</t>
+          <t>피처 계약 조회</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1945,14 +1945,14 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>dataset_name, source_type, population_filter</t>
+          <t>feature_definition_id, required, missing_value_policy</t>
         </is>
       </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>모델 관리(내부) [POST-MVP]</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/experiments</t>
+          <t>/admin/training-datasets</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>실험 기록</t>
+          <t>학습 데이터셋 등록</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1977,29 +1977,29 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>algorithm, split_config, preprocessing_config</t>
+          <t>dataset_name, source_type, population_filter</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>모델 관리(내부) [POST-MVP]</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>/admin/experiments/{experiment_id}/metrics</t>
+          <t>/admin/models/versions/{version_id}/experiments</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>성능지표·혼동행렬 조회</t>
+          <t>실험 기록</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>model_experiment_metrics[], model_confusion_matrices</t>
+          <t>algorithm, split_config, preprocessing_config</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>모델 관리(내부) [POST-MVP]</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>/admin/feature-weights/versions</t>
+          <t>/admin/experiments/{experiment_id}/metrics</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>피처 가중치 버전 이력</t>
+          <t>성능지표·혼동행렬 조회</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2041,14 +2041,14 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>version, reason, effective_from</t>
+          <t>model_experiment_metrics[], model_confusion_matrices</t>
         </is>
       </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그</t>
+          <t>모델 관리(내부)</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>/challenge-categories</t>
+          <t>/admin/feature-weights/versions</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>챌린지 카테고리 목록</t>
+          <t>피처 가중치 버전 이력</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>관리자</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>category_code, category_name</t>
+          <t>version, reason, effective_from</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>/challenges</t>
+          <t>/challenge-categories</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>챌린지 목록(카테고리 필터)</t>
+          <t>챌린지 카테고리 목록</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
+          <t>category_code, category_name</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2122,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}</t>
+          <t>/challenges</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>챌린지 상세(근거자료 포함)</t>
+          <t>챌린지 목록(카테고리 필터)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>description, evidence_sources[](title, source_url, citation_text)</t>
+          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}/levels</t>
+          <t>/challenges/{challenge_id}</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>난이도별 목표 조회(상/중/하)</t>
+          <t>챌린지 상세(v5: 근거출처 배지 제거됨)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2169,29 +2169,29 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>difficulty(low/medium/high), weekly_target, target_config</t>
+          <t>description (evidence_sources는 식단분석 전용으로 이동)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>챌린지 추천</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations</t>
+          <t>/challenges/{challenge_id}/levels</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>추천 배치 생성(설문+예측 기반)</t>
+          <t>난이도별 목표 조회(상/중/하)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
+          <t>difficulty(low/medium/high), weekly_target, target_config</t>
         </is>
       </c>
     </row>
@@ -2213,17 +2213,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}</t>
+          <t>/challenge-recommendations</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>추천 후보+이유 조회</t>
+          <t>추천 배치 생성(설문+예측 기반)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
+          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
         </is>
       </c>
     </row>
@@ -2245,17 +2245,17 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}/view</t>
+          <t>/challenge-recommendations/{batch_id}</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>추천 결과 열람 처리</t>
+          <t>추천 후보+이유 조회</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2265,14 +2265,14 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>viewed_at 기록</t>
+          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
         </is>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>챌린지 추천</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles</t>
+          <t>/challenge-recommendations/{batch_id}/view</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>4주 사이클 시작</t>
+          <t>추천 결과 열람 처리</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
+          <t>viewed_at 기록</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/active</t>
+          <t>/challenge-cycles</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>진행중 사이클 조회</t>
+          <t>4주 사이클 시작</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>started_on, ended_on, cycle_challenges[]</t>
+          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
         </is>
       </c>
     </row>
@@ -2341,17 +2341,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/stop</t>
+          <t>/challenge-cycles/active</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>사이클 중단</t>
+          <t>진행중 사이클 조회</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>stopped_reason_code, stopped_note</t>
+          <t>started_on, ended_on, cycle_challenges[]</t>
         </is>
       </c>
     </row>
@@ -2373,17 +2373,17 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/weeks</t>
+          <t>/challenge-cycles/{cycle_id}/stop</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>주차별 목표·달성 현황</t>
+          <t>사이클 중단</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>week_number, target_count, achieved_count</t>
+          <t>stopped_reason_code, stopped_note</t>
         </is>
       </c>
     </row>
@@ -2405,17 +2405,17 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>/cycle-challenges/{id}/logs</t>
+          <t>/challenge-cycles/{cycle_id}/weeks</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>일일 수행 기록</t>
+          <t>주차별 목표·달성 현황</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>log_date, status, quantity</t>
+          <t>week_number, target_count, achieved_count</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>/challenge-logs/{log_id}/proofs</t>
+          <t>/cycle-challenges/{id}/logs</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>인증자료 첨부</t>
+          <t>일일 수행 기록</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2457,14 +2457,14 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>proof_type, file_job_id, proof_data</t>
+          <t>log_date, status, quantity</t>
         </is>
       </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>식단 분석</t>
+          <t>챌린지 사이클·수행</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses</t>
+          <t>/challenge-logs/{log_id}/proofs</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>식단 사진 분석 요청</t>
+          <t>인증자료 첨부</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
+          <t>proof_type, file_job_id, proof_data</t>
         </is>
       </c>
     </row>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses/{id}</t>
+          <t>/meal-analyses</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>분석 결과 조회(나트륨 점수)</t>
+          <t>식단 사진 분석 요청</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>sodium_score, meal_analysis_foods[]</t>
+          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>/food-items/search</t>
+          <t>/meal-analyses/{id}</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>음식명 검색(수동 등록용)</t>
+          <t>분석 결과 조회(나트륨 점수)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2553,14 +2553,14 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>food_name, sodium_mg</t>
+          <t>sodium_score, meal_analysis_foods[]</t>
         </is>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>식단 분석</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notification-preferences</t>
+          <t>/food-items/search</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 조회</t>
+          <t>음식명 검색(수동 등록용)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time, timezone</t>
+          <t>food_name, sodium_mg, evidence_source_id</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 변경</t>
+          <t>알림 설정 조회</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time</t>
+          <t>push_enabled, morning_time, timezone</t>
         </is>
       </c>
     </row>
@@ -2629,17 +2629,17 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices</t>
+          <t>/users/me/notification-preferences</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록</t>
+          <t>알림 설정 변경</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>endpoint, public_key, auth_key</t>
+          <t>push_enabled, morning_time</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices/{id}</t>
+          <t>/users/me/push-devices</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록 해제</t>
+          <t>푸시 토큰 등록</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>revoked_at 기록</t>
+          <t>endpoint, public_key, auth_key</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notifications</t>
+          <t>/users/me/push-devices/{id}</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>발송 내역 조회</t>
+          <t>푸시 토큰 등록 해제</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2713,29 +2713,29 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>notification_deliveries[](status, sent_at)</t>
+          <t>revoked_at 기록</t>
         </is>
       </c>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>피드백</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>/feedbacks</t>
+          <t>/users/me/notifications</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>피드백 등록(예측·추천·사이클 대상)</t>
+          <t>발송 내역 조회</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
+          <t>notification_deliveries[](status, sent_at)</t>
         </is>
       </c>
     </row>
@@ -2757,17 +2757,17 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>/users/me/feedbacks</t>
+          <t>/feedbacks</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>내가 남긴 피드백 목록</t>
+          <t>피드백 등록(예측·추천·사이클 대상)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>feedback_type, rating, created_at</t>
+          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
         </is>
       </c>
     </row>
@@ -2794,22 +2794,22 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>/admin/feedback-reports</t>
+          <t>/users/me/feedbacks</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>피드백 분석 리포트 조회</t>
+          <t>내가 남긴 피드백 목록</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>period_start, period_end, result_json</t>
+          <t>feedback_type, rating, created_at</t>
         </is>
       </c>
     </row>
@@ -2826,27 +2826,59 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>/admin/feedback-reports/{id}/actions</t>
+          <t>/admin/feedback-reports [POST-MVP]</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
+          <t>피드백 분석 리포트 조회</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>period_start, period_end, result_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>/admin/feedback-reports/{id}/actions [POST-MVP]</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
           <t>개선 조치 이력 조회</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>feature_area, proposed_action, status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F74"/>
+  <autoFilter ref="A1:F75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3163,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3190,7 +3222,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>diagnosed_hypertension=true 또는 age_eligible=false면 예측 API 이용 불가, 챌린지·기록은 이용 가능. [확정] emergency_flag=true여도 진행 차단 안 함(REQ-ELIG-003), 대신 '주치의 연락' 팝업 노출.</t>
+          <t>[v5 갱신] emergency_flag=true(예/잘모르겠음)면 119 버튼 노출 + '그래도 진행' 확인 필요. 확인 시각은 emergency_acknowledged_at에 저장, 신규 엔드포인트로 처리. 확인 전엔 건강정보·예측 API 403. diagnosed_hypertension은 더 이상 제외 트리거가 아니라 모델 A 입력 피처로 사용(단, CVD 자체 진단 제외 여부는 아직 미정).</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3246,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>나트륨 5문항 합산 0~10점 → 하(0~3,≤2088mg)/중(4~6)/상(7~10,&gt;3363mg) 3등급 변환(REQ-PRED-008, KNHANES 삼분위수 기준).</t>
+          <t>나트륨 5문항 합산 0~10점 → 하(0~3,≤2088mg)/중(4~6)/상(7~10,&gt;3363mg) 3등급 변환(REQ-PRED-008, KNHANES 삼분위수 기준). [v5] 모델 B 삭제로 이 점수의 최종 목적지 재확인 필요(챌린지 추천 로직 추정).</t>
         </is>
       </c>
     </row>
@@ -3233,36 +3265,72 @@
     <row r="6" ht="60" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>모델 관리</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>고정 2(흡연·음주)+선택 1=총 3개 확정(REQ-CHAL-003). 비흡연·비음주자는 나트륨으로 대체(REQ-CHAL-008). 지난 날짜 로그 수정은 403(REQ-CHAL-005). 음주는 남2/여1잔 초과시 경고+실패 처리(REQ-CHAL-010).</t>
+          <t>[v5] 모델 B 완전 삭제. 운영 모델은 MODEL_A 1종(10년 후 관상동맥질환/CHD, 기존 '10년 후 고혈압'에서 정정). training_datasets/model_experiments/model_experiment_metrics 관련 엔드포인트는 POST-MVP.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>reevaluation_schedules.schedule_type(enum reevaluation_type) = interim_4week / full_3to6month. health_records.input_type과는 별개 enum이니 혼용 주의.</t>
+          <t>[v5] REQ-CHAL-011 삭제로 챌린지 상세 응답에서 근거출처(evidence_sources) 배지 제거. evidence_sources는 이제 식단분석(food_items) 전용.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>챌린지 사이클·수행</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>고정 2(흡연·음주)+선택 1=총 3개 확정(REQ-CHAL-003). 비흡연·비음주자는 modifiable=true이고 risk 기여도가 가장 큰 요인의 미션으로 대체, 그중 나트륨이 후보 1순위(REQ-CHAL-008). 지난 날짜 로그 수정은 403(REQ-CHAL-005). 음주는 남2/여1잔 초과시 경고+실패 처리(REQ-CHAL-010).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>알림</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>reevaluation_schedules.schedule_type(enum reevaluation_type) = interim_4week / full_3to6month. health_records.input_type과는 별개 enum이니 혼용 주의.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>피드백</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>feedback_type = prediction_rating / recommendation_rating / challenge_difficulty(쉬움·적당·어려움, REQ-FEED-002) / recommendation_reject_reason(REQ-FEED-003).</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>feedback_type = prediction_rating / recommendation_rating / challenge_difficulty(쉬움·적당·어려움, REQ-FEED-002) / recommendation_reject_reason(REQ-FEED-003). [v5] 리포트·개선조치 조회 2개는 POST-MVP, 등록/목록조회 2개만 이번 스프린트 대상.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>운영·감사 로그</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>[v5] service_health_checks 테이블 삭제 — GET /admin/health는 저장 없이 실시간으로 DB·큐 상태를 점검해 응답. api_request_audits는 POST-MVP, analytics_events·security_audit_logs만 이번 스프린트에서 적재.</t>
         </is>
       </c>
     </row>

--- a/docs/api-spec/PAEON_API_명세서.xlsx
+++ b/docs/api-spec/PAEON_API_명세서.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도메인별 비고" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API 명세서'!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API 명세서'!$A$1:$F$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>answers[](question_code, answer_code) → result_code, age_eligible, diagnosed_hypertension, emergency_flag</t>
+          <t>answers[] → result_code(eligible/age_out/diagnosed/emergency), age_eligible, diagnosed_cad(v8: 이름변경, 관상동맥질환 기진단), emergency_flag</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>→ emergency_acknowledged_at 기록</t>
+          <t>→ emergency_acknowledged_at 기록. 모델별 연령범위 다름: A=32~70세, B=19세+(고혈압진단 제외)</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>예측 결과 상세</t>
+          <t>예측 결과 상세 [정정: 모델A·B 둘다 운영중]</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>risk_level, score, vascular_age, prediction_factors[]</t>
+          <t>model_code, model_version, risk_level, score, vascular_age(A만), prediction_factors[](direction_matches_expectation 포함), missing_features[]</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>prediction_id, predicted_at</t>
+          <t>model_code별 배열(최대 2개)</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>질환별 모델 목록 — v5: MODEL_A만 운영(모델B 삭제)</t>
+          <t>질환별 모델 목록 [정정: MODEL_A·MODEL_B 둘다 운영중, 삭제 아님]</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그</t>
+          <t>모델 관리(내부)</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2090,54 +2090,54 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>/challenge-categories</t>
+          <t>/admin/factor-challenge-links</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>챌린지 카테고리 목록</t>
+          <t>요인↔챌린지 연결 큐레이션(v8 신규)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>관리자</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>category_code, category_name</t>
+          <t>model_id, factor_code, category_id, link_status(linked/pending_decision/not_linked)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그</t>
+          <t>모델 관리(내부)</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>/challenges</t>
+          <t>/admin/factor-challenge-links/{factor_link_id}</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>챌린지 목록(카테고리 필터)</t>
+          <t>연결 상태 확정</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>관리자</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
+          <t>link_status, category_id, note</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2154,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}</t>
+          <t>/challenge-categories</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>챌린지 상세(v5: 근거출처 배지 제거됨)</t>
+          <t>챌린지 카테고리 목록</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>description (evidence_sources는 식단분석 전용으로 이동)</t>
+          <t>category_code, category_name, catalog_status(mvp/review/backlog — v8: 아침식사=review, 체중관리=backlog)</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}/levels</t>
+          <t>/challenges</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>난이도별 목표 조회(상/중/하)</t>
+          <t>챌린지 목록(카테고리 필터)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2201,29 +2201,29 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>difficulty(low/medium/high), weekly_target, target_config</t>
+          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
         </is>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>챌린지 추천</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations</t>
+          <t>/challenges/{challenge_id}</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>추천 배치 생성(설문+예측 기반)</t>
+          <t>챌린지 상세(v5: 근거출처 배지 제거됨)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2233,14 +2233,14 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
+          <t>description (evidence_sources는 식단분석 전용으로 이동)</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>챌린지 추천</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}</t>
+          <t>/challenges/{challenge_id}/levels</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>추천 후보+이유 조회</t>
+          <t>난이도별 목표 조회(상/중/하)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
+          <t>difficulty(low/medium/high), weekly_target, target_config</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}/view</t>
+          <t>/challenge-recommendations</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>추천 결과 열람 처리</t>
+          <t>추천 배치 생성(설문+예측 기반)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2297,29 +2297,29 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>viewed_at 기록</t>
+          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>챌린지 추천</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles</t>
+          <t>/challenge-recommendations/{batch_id}</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>4주 사이클 시작</t>
+          <t>추천 후보+이유 조회</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2329,29 +2329,29 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
+          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
         </is>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>챌린지 추천</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/active</t>
+          <t>/challenge-recommendations/{batch_id}/view</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>진행중 사이클 조회</t>
+          <t>추천 결과 열람 처리</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>started_on, ended_on, cycle_challenges[]</t>
+          <t>viewed_at 기록</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/stop</t>
+          <t>/challenge-cycles</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>사이클 중단</t>
+          <t>4주 사이클 시작</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>stopped_reason_code, stopped_note</t>
+          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/weeks</t>
+          <t>/challenge-cycles/active</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>주차별 목표·달성 현황</t>
+          <t>진행중 사이클 조회</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>week_number, target_count, achieved_count</t>
+          <t>started_on, ended_on, cycle_challenges[]</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>/cycle-challenges/{id}/logs</t>
+          <t>/challenge-cycles/{cycle_id}/stop</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>일일 수행 기록</t>
+          <t>사이클 중단</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>log_date, status, quantity</t>
+          <t>stopped_reason_code, stopped_note</t>
         </is>
       </c>
     </row>
@@ -2469,17 +2469,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>/challenge-logs/{log_id}/proofs</t>
+          <t>/challenge-cycles/{cycle_id}/weeks</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>인증자료 첨부</t>
+          <t>주차별 목표·달성 현황</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2489,14 +2489,14 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>proof_type, file_job_id, proof_data</t>
+          <t>week_number, target_count, achieved_count</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>식단 분석</t>
+          <t>챌린지 사이클·수행</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses</t>
+          <t>/cycle-challenges/{id}/logs</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>식단 사진 분석 요청</t>
+          <t>일일 수행 기록</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2521,29 +2521,29 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
+          <t>log_date, status, quantity</t>
         </is>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>식단 분석</t>
+          <t>챌린지 사이클·수행</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses/{id}</t>
+          <t>/challenge-logs/{log_id}/proofs</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>분석 결과 조회(나트륨 점수)</t>
+          <t>인증자료 첨부</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>sodium_score, meal_analysis_foods[]</t>
+          <t>proof_type, file_job_id, proof_data</t>
         </is>
       </c>
     </row>
@@ -2565,17 +2565,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>/food-items/search</t>
+          <t>/meal-analyses</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>음식명 검색(수동 등록용)</t>
+          <t>식단 사진 분석 요청</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2585,14 +2585,14 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>food_name, sodium_mg, evidence_source_id</t>
+          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>식단 분석</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notification-preferences</t>
+          <t>/meal-analyses/{id}</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 조회</t>
+          <t>분석 결과 조회(나트륨 점수)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2617,29 +2617,29 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time, timezone</t>
+          <t>sodium_score, meal_analysis_foods[]</t>
         </is>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>식단 분석</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notification-preferences</t>
+          <t>/food-items/search</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 변경</t>
+          <t>음식명 검색(수동 등록용)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time</t>
+          <t>food_name, sodium_mg, evidence_source_id</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices</t>
+          <t>/users/me/notification-preferences</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록</t>
+          <t>알림 설정 조회</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>endpoint, public_key, auth_key</t>
+          <t>push_enabled, morning_time, timezone</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices/{id}</t>
+          <t>/users/me/notification-preferences</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록 해제</t>
+          <t>알림 설정 변경</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>revoked_at 기록</t>
+          <t>push_enabled, morning_time</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2725,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notifications</t>
+          <t>/users/me/push-devices</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>발송 내역 조회</t>
+          <t>푸시 토큰 등록</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2745,29 +2745,29 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>notification_deliveries[](status, sent_at)</t>
+          <t>endpoint, public_key, auth_key</t>
         </is>
       </c>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>피드백</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>/feedbacks</t>
+          <t>/users/me/push-devices/{id}</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>피드백 등록(예측·추천·사이클 대상)</t>
+          <t>푸시 토큰 등록 해제</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
+          <t>revoked_at 기록</t>
         </is>
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>피드백</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>/users/me/feedbacks</t>
+          <t>/users/me/notifications</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>내가 남긴 피드백 목록</t>
+          <t>발송 내역 조회</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>feedback_type, rating, created_at</t>
+          <t>notification_deliveries[](status, sent_at)</t>
         </is>
       </c>
     </row>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>/admin/feedback-reports [POST-MVP]</t>
+          <t>/feedbacks</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>피드백 분석 리포트 조회</t>
+          <t>피드백 등록(예측·추천·사이클 대상)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>period_start, period_end, result_json</t>
+          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
         </is>
       </c>
     </row>
@@ -2858,27 +2858,91 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
+          <t>/users/me/feedbacks</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>내가 남긴 피드백 목록</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>필요</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>feedback_type, rating, created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>/admin/feedback-reports [POST-MVP]</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>피드백 분석 리포트 조회</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>period_start, period_end, result_json</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>피드백</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
           <t>/admin/feedback-reports/{id}/actions [POST-MVP]</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>개선 조치 이력 조회</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>feature_area, proposed_action, status</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F75"/>
+  <autoFilter ref="A1:F77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3222,7 +3286,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>[v5 갱신] emergency_flag=true(예/잘모르겠음)면 119 버튼 노출 + '그래도 진행' 확인 필요. 확인 시각은 emergency_acknowledged_at에 저장, 신규 엔드포인트로 처리. 확인 전엔 건강정보·예측 API 403. diagnosed_hypertension은 더 이상 제외 트리거가 아니라 모델 A 입력 피처로 사용(단, CVD 자체 진단 제외 여부는 아직 미정).</t>
+          <t>[v8 확정] emergency_flag=true(예/잘모르겠음)면 119 버튼 + '그래도 진행' 확인 필요(emergency_acknowledged_at). diagnosed_hypertension→diagnosed_cad로 이름변경(관상동맥질환 기진단만 제외 트리거). 고혈압 진단은 health_measurements.HTN_STATUS로 이동, 모델A 입력피처(모델B는 고혈압진단자 제외). 모델별 연령범위: A=32~70, B=19+(상한없음,80+는 80으로 계산).</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3298,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>재입력 2주기(REQ-HEALTH-008): input_type = initial/interim_reassessment/full_reassessment/weekly_bp/manual. 주1회 혈압은 매번 새 레코드(input_type=weekly_bp)로 생성. interim_reassessment 시 콜레스테롤 등은 input_method=carried_forward로 이전 값 승계.</t>
+          <t>재입력 2주기(REQ-HEALTH-008): input_type = initial/interim_reassessment/full_reassessment/weekly_bp/manual. [v8] metric_code 확정: 필수 13종(SBP,DBP,HEIGHT,WEIGHT,WAIST,SMOKING,ALCOHOL_FREQ,ALCOHOL_AMOUNT,DIABETES,HTN_STATUS,TOTAL_CHOL,HDL,PARENT_HTN)+선택2종+계산2종. 허리둘레·1회음주량은 모델B용 v8 신규 필수항목.</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3310,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>나트륨 5문항 합산 0~10점 → 하(0~3,≤2088mg)/중(4~6)/상(7~10,&gt;3363mg) 3등급 변환(REQ-PRED-008, KNHANES 삼분위수 기준). [v5] 모델 B 삭제로 이 점수의 최종 목적지 재확인 필요(챌린지 추천 로직 추정).</t>
+          <t>나트륨 5문항 합산 0~10점 → 하(0~3,≤2088mg)/중(4~6)/상(7~10,&gt;3363mg) 3등급 변환(REQ-PRED-008, KNHANES 삼분위수 기준). 이 점수의 최종 용도는 담당자 확인 필요(모델B 실제 피처 12개엔 이 합산점수 없음).</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3322,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>수동 재예측(request_type=manual)은 사이클당 7일 1회 제한, 초과시 429. 자동 재예측(사이클 종료시)은 제한 무관.</t>
+          <t>수동 재예측(request_type=manual)은 사이클당 7일 1회 제한, 초과시 429. 모델A 원시확률 노출 금지, 모델B는 '현재 유사도'로만 표현. 위험판정은 입력혈압규칙(HE_HP)기준.</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3334,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>[v5] 모델 B 완전 삭제. 운영 모델은 MODEL_A 1종(10년 후 관상동맥질환/CHD, 기존 '10년 후 고혈압'에서 정정). training_datasets/model_experiments/model_experiment_metrics 관련 엔드포인트는 POST-MVP.</t>
+          <t>모델A(Framingham,CHD,32~70세,피처9개,AUC0.701)·모델B(KNHANES,경계군유사도,19세+,피처12개,AUC0.745) 둘다 운영중. 두 모델 확률 합산·평균 금지(REQ-PRED-006). [v8 해결] 모델B 반대방향 요인(흡연·외식·운동) 문제는 factor_challenge_links 테이블로 요인별 큐레이션(linked/pending_decision/not_linked)하여 해결. 대체 미션은 모델B가 아닌 모델A의 SHAP상위5 요인 중 linked인 것만 채택.</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3346,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>[v5] REQ-CHAL-011 삭제로 챌린지 상세 응답에서 근거출처(evidence_sources) 배지 제거. evidence_sources는 이제 식단분석(food_items) 전용.</t>
+          <t>[v8] challenge_categories에 catalog_status(mvp/review/backlog) 추가 — 아침식사 카테고리는 review(근거 재검토 중), 체중관리는 backlog(미출시)로 명시적 추적됨. (v5: REQ-CHAL-011 삭제로 근거출처 배지도 제거, evidence_sources는 식단분석 전용)</t>
         </is>
       </c>
     </row>

--- a/docs/api-spec/PAEON_API_명세서.xlsx
+++ b/docs/api-spec/PAEON_API_명세서.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API 명세서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공통 규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="도메인별 비고" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="API 명세서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="공통 규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="도메인별 비고" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="변경 이력" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'API 명세서'!$A$1:$F$77</definedName>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +44,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -84,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -99,6 +104,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -466,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1125,17 +1136,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/eligibility/assessments</t>
+          <t>/users/me/eligibility</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>적합성 문진 제출</t>
+          <t>[v8.1 수정] 대상 확인 답 저장(만 나이 범위·관상동맥질환 진단·응급 증상)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1145,7 +1156,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>answers[] → result_code(eligible/age_out/diagnosed/emergency), age_eligible, diagnosed_cad(v8: 이름변경, 관상동맥질환 기진단), emergency_flag</t>
+          <t>age_eligible, diagnosed_cad(관상동맥질환 진단 → 모델 A 제외), emergency_flag, emergency_acknowledged → result_code, assessed_at, emergency_acknowledged_at. 모델별 연령: A 32~70세, B 19세 이상(고혈압 진단·치료 중이면 B 제외)</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1173,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/eligibility/assessments/latest</t>
+          <t>/users/me/eligibility</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>최근 판정 결과 조회</t>
+          <t>[v8.1 수정] 저장된 대상 확인 답 조회</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1177,29 +1188,29 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>result_code, assessed_at</t>
+          <t>result_code, age_eligible, diagnosed_cad, emergency_flag, emergency_acknowledged_at, assessed_at</t>
         </is>
       </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>이용 적합성</t>
+          <t>건강정보 입력</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/eligibility/assessments/{assessment_id}/acknowledge-emergency</t>
+          <t>/health/schemas/active</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>응급 안내 확인 후 계속 진행(v5 신규)</t>
+          <t>현재 사용중인 입력 스키마 조회</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1209,7 +1220,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>→ emergency_acknowledged_at 기록. 모델별 연령범위 다름: A=32~70세, B=19세+(고혈압진단 제외)</t>
+          <t>schema_version, model_scope</t>
         </is>
       </c>
     </row>
@@ -1221,17 +1232,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/health/schemas/active</t>
+          <t>/health/records</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>현재 사용중인 입력 스키마 조회</t>
+          <t>건강기록 신규 생성</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1241,7 +1252,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>schema_version, model_scope</t>
+          <t>health_schema_id, input_type(initial/interim_reassessment/full_reassessment/weekly_bp/manual), examination_date, alcohol_frequency(필수로 변경)</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1269,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/health/records</t>
+          <t>/health/records/{id}/measurements</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>건강기록 신규 생성</t>
+          <t>측정값 일괄 등록</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1273,7 +1284,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>health_schema_id, input_type(initial/interim_reassessment/full_reassessment/weekly_bp/manual), examination_date, alcohol_frequency(필수로 변경)</t>
+          <t>metric_code, value_num, unit, measured_on</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1296,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/health/records/{id}/measurements</t>
+          <t>/health/records/{id}</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>측정값 일괄 등록</t>
+          <t>건강기록 상세 (측정값+검증오류 포함)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1305,7 +1316,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>metric_code, value_num, unit, measured_on</t>
+          <t>health_measurements[], health_validation_errors[]</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1333,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>/health/records/{id}</t>
+          <t>/health/records</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>건강기록 상세 (측정값+검증오류 포함)</t>
+          <t>건강기록 이력 목록</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1337,7 +1348,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>health_measurements[], health_validation_errors[]</t>
+          <t>examination_date, verified_at</t>
         </is>
       </c>
     </row>
@@ -1349,17 +1360,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>/health/records</t>
+          <t>/health/files</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>건강기록 이력 목록</t>
+          <t>검진결과지 업로드</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1369,7 +1380,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>examination_date, verified_at</t>
+          <t>file_purpose, storage_object_key → file_job_id</t>
         </is>
       </c>
     </row>
@@ -1381,17 +1392,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/health/files</t>
+          <t>/health/files/{file_job_id}</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>검진결과지 업로드</t>
+          <t>업로드·OCR 처리 상태 조회</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1401,7 +1412,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>file_purpose, storage_object_key → file_job_id</t>
+          <t>status, ocr_extraction_results[]</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1424,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>/health/files/{file_job_id}</t>
+          <t>/health/files/{file_job_id}/ocr-results/{extraction_result_id}/accept</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>업로드·OCR 처리 상태 조회</t>
+          <t>OCR 추출값 확정 반영</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1433,29 +1444,29 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>status, ocr_extraction_results[]</t>
+          <t>accepted_by_user=true → health_measurements 반영</t>
         </is>
       </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>건강정보 입력</t>
+          <t>설문</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>/health/files/{file_job_id}/ocr-results/{extraction_result_id}/accept</t>
+          <t>/surveys/{survey_type}/active</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>OCR 추출값 확정 반영</t>
+          <t>활성 설문 버전+문항+옵션 조회</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1465,7 +1476,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>accepted_by_user=true → health_measurements 반영</t>
+          <t>survey_version_id, survey_questions[], survey_options[]</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1488,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>/surveys/{survey_type}/active</t>
+          <t>/survey-instances</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>활성 설문 버전+문항+옵션 조회</t>
+          <t>설문 응답 세션 시작</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1497,7 +1508,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>survey_version_id, survey_questions[], survey_options[]</t>
+          <t>survey_version_id, health_record_id → survey_instance_id</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1525,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances</t>
+          <t>/survey-instances/{id}/responses</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>설문 응답 세션 시작</t>
+          <t>문항 응답 저장(배치)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1529,7 +1540,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>survey_version_id, health_record_id → survey_instance_id</t>
+          <t>question_id, option_ids[](단일 1개/복수 N개), answer_json</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1557,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}/responses</t>
+          <t>/survey-instances/{id}/submit</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>문항 응답 저장(배치)</t>
+          <t>설문 제출 확정</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1561,7 +1572,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>question_id, option_ids[](단일 1개/복수 N개), answer_json</t>
+          <t>submitted_at 기록</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1584,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}/submit</t>
+          <t>/survey-instances/{id}</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>설문 제출 확정</t>
+          <t>응답 현황 조회</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1593,29 +1604,29 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>submitted_at 기록</t>
+          <t>status, survey_responses[]</t>
         </is>
       </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>설문</t>
+          <t>예측 실행·결과</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>/survey-instances/{id}</t>
+          <t>/predictions/jobs</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>응답 현황 조회</t>
+          <t>[v8.1 수정] 예측 실행(요청 즉시 계산해 결과 반환). [확인 요청: 백엔드] 비동기 접수(202) 여부는 요구사항 REQ-PRED-002 결정 후</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1625,7 +1636,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>status, survey_responses[]</t>
+          <t>health_record_id, survey_instance_id, request_type(initial/interim/full/manual) → 201 prediction_job_id, status, model_a, model_b, disclaimer (결과 형식은 아래 /predictions/{prediction_job_id})</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1648,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>/predictions/jobs</t>
+          <t>/predictions/jobs/{job_id}</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>예측 실행 요청(비동기)</t>
+          <t>작업 상태 조회(폴링). [확인 요청: 백엔드] 구현 없음(예측이 즉시 끝남). REQ-PRED-002 결정 후 삭제 또는 유지</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1657,7 +1668,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>health_record_id, request_type(auto/manual) → job_id, status</t>
+          <t>status, prediction_job_runs[]</t>
         </is>
       </c>
     </row>
@@ -1674,12 +1685,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>/predictions/jobs/{job_id}</t>
+          <t>/predictions/{prediction_job_id}</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>작업 상태 조회(폴링)</t>
+          <t>[v8.1 수정] 예측 결과 상세(번호표 기준, 모델 A·B 각각)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1689,7 +1700,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>status, prediction_job_runs[]</t>
+          <t>prediction_job_id, status, disclaimer, model_a·model_b { model_code, model_version, status(completed/skipped/failed), skip_reason(age_out_of_range / cad_diagnosed / htn_diagnosed), probability(A: 한국인 보정 10년 확률, 화면에 "생활습관 관리용 참고 신호"로 % 표시 / B: 화면에 숫자 비표시), risk_level(A만 normal·borderline·high = 양호 &lt;2%·주의 2~9%·높음 ≥9%), percentile(A만, 같은 성별·연령대 상위 %), vascular_age(A만), similarity_level(B만 similar·slightly_different·different), factors[](direction_matches_expectation 포함), top_risk_factor, top_modifiable_factor, missing_features[] }</t>
         </is>
       </c>
     </row>
@@ -1706,12 +1717,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>/predictions/{prediction_id}</t>
+          <t>/predictions/latest</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>예측 결과 상세 [정정: 모델A·B 둘다 운영중]</t>
+          <t>[v8.1 수정] 최신 예측 결과 조회</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1721,7 +1732,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>model_code, model_version, risk_level, score, vascular_age(A만), prediction_factors[](direction_matches_expectation 포함), missing_features[]</t>
+          <t>/predictions/{prediction_job_id}와 같은 형식</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1749,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>/predictions/latest</t>
+          <t>/predictions</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>최신 예측 결과 조회</t>
+          <t>[v8.1 수정] 예측 이력 목록(추이)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1753,14 +1764,14 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>model_code별 배열(최대 2개)</t>
+          <t>prediction_job_id, request_type, examination_date, completed_at, model_a·model_b 요약 { status, model_version, risk_level, percentile, vascular_age, similarity_level, skip_reason }</t>
         </is>
       </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>예측 실행·결과</t>
+          <t>예측 실행·결과 [POST-MVP]</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1770,12 +1781,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>/predictions</t>
+          <t>/predictions/{prediction_id}/disclosures</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>예측 이력 목록(추이)</t>
+          <t>[POST-MVP v8.1] 안전 고지 문구 조회. 지금은 예측 응답의 disclaimer와 화면 고정 문구(확률 근거·계산 근거·비교 기준). 필요한 이유: 고지 문구 버전별 노출 기록(ERD result_disclosures)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1785,7 +1796,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>score, vascular_age, predicted_at[]</t>
+          <t>disclosure_type, message_version</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1813,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>/predictions/{prediction_id}/disclosures</t>
+          <t>/reassessments/latest</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>안전 고지 문구 조회</t>
+          <t>[v8.1 신규] 최근 4주 재입력 전·후 모델 결과 비교</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1817,110 +1828,110 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>disclosure_type, message_version</t>
+          <t>baseline_job_id, interim_job_id, baseline_date, interim_date, measurements, weekly_bp, model_a·model_b { comparable, reason(missing/skipped/model_version_changed), before, after }</t>
         </is>
       </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>예측 실행·결과</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>/admin/models</t>
+          <t>/predict</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>질환별 모델 목록 [정정: MODEL_A·MODEL_B 둘다 운영중, 삭제 아님]</t>
+          <t>[v8.1 신규] [임시] 모델 연결 확인용. 저장하지 않음</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>disease_id, model_code, prediction_scope</t>
+          <t>나이·성별·건강정보(PredictRequest) → model_a, model_b, disclaimer</t>
         </is>
       </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>예측 실행·결과</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/{model_id}/versions</t>
+          <t>/challenges/cycles/{cycle_id}/review</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>신규 모델 버전 등록</t>
+          <t>[v8.1 신규] 4주 전·후 비교 중 모델 부분</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>artifact_uri, preprocessing_version, threshold_config</t>
+          <t>models[] { model_code, model_version, comparable, reason, before/after_status, before/after_risk_level, before/after_probability, before/after_percentile, before/after_similarity_level }. 나머지 필드(missions, before/after 측정값 등)는 챌린지 담당</t>
         </is>
       </c>
     </row>
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>예측 실행·결과</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/activate</t>
+          <t>/challenges/program/review</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>버전 활성화</t>
+          <t>[v8.1 신규] 12주 처음↔마지막 비교 중 모델 부분</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>released_at 기록, 기존 버전 retired_at</t>
+          <t>models[] (위와 같은 형식). weeks_done, checkpoints, cycles는 챌린지 담당</t>
         </is>
       </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>모델 관리(내부) [POST-MVP]</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1930,12 +1941,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/feature-contracts</t>
+          <t>/admin/models</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>피처 계약 조회</t>
+          <t>[POST-MVP v8.1] 질환별 모델 목록. 지금은 모델 JSON(modeling/*/artifacts)과 git으로 관리. 필요해지는 조건: 식약처 의료기기 판정 시 변경관리, 질환·모델 추가</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1945,7 +1956,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>feature_definition_id, required, missing_value_policy</t>
+          <t>disease_id, model_code, prediction_scope</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1973,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>/admin/training-datasets</t>
+          <t>/admin/models/{model_id}/versions</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>학습 데이터셋 등록</t>
+          <t>[POST-MVP v8.1] 신규 모델 버전 등록. 지금은 모델 JSON(modeling/*/artifacts)과 git으로 관리. 필요해지는 조건: 식약처 의료기기 판정 시 변경관리, 질환·모델 추가</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1977,7 +1988,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>dataset_name, source_type, population_filter</t>
+          <t>artifact_uri, preprocessing_version, threshold_config</t>
         </is>
       </c>
     </row>
@@ -1994,12 +2005,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>/admin/models/versions/{version_id}/experiments</t>
+          <t>/admin/models/versions/{version_id}/activate</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>실험 기록</t>
+          <t>[POST-MVP v8.1] 버전 활성화. 지금은 모델 JSON(modeling/*/artifacts)과 git으로 관리. 필요해지는 조건: 식약처 의료기기 판정 시 변경관리, 질환·모델 추가</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2009,14 +2020,14 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>algorithm, split_config, preprocessing_config</t>
+          <t>released_at 기록, 기존 버전 retired_at</t>
         </is>
       </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부) [POST-MVP]</t>
+          <t>모델 관리(내부)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2026,12 +2037,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>/admin/experiments/{experiment_id}/metrics</t>
+          <t>/admin/models/versions/{version_id}/feature-contracts</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>성능지표·혼동행렬 조회</t>
+          <t>[v8.1 삭제 예정] 피처 계약 조회. 모델 입력 계약은 모델 JSON과 modeling/handoff/모델_연결_명세.md가 담당</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2041,7 +2052,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>model_experiment_metrics[], model_confusion_matrices</t>
+          <t>feature_definition_id, required, missing_value_policy</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2074,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>피처 가중치 버전 이력</t>
+          <t>[v8.1 삭제 예정] 피처 가중치 버전 이력. 피드백 기반 가중치 보정을 하지 않음(NFR-FEED-002 v2.3). [확인 요청: 챌린지 담당] 추천 배치가 참조</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -2080,7 +2091,7 @@
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2090,54 +2101,54 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>/admin/factor-challenge-links</t>
+          <t>/challenge-categories</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>요인↔챌린지 연결 큐레이션(v8 신규)</t>
+          <t>챌린지 카테고리 목록</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>model_id, factor_code, category_id, link_status(linked/pending_decision/not_linked)</t>
+          <t>category_code, category_name, catalog_status(mvp/review/backlog — v8: 아침식사=review, 체중관리=backlog)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="32" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>모델 관리(내부)</t>
+          <t>챌린지 카탈로그</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>/admin/factor-challenge-links/{factor_link_id}</t>
+          <t>/challenges</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>연결 상태 확정</t>
+          <t>챌린지 목록(카테고리 필터)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>관리자</t>
+          <t>필요</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>link_status, category_id, note</t>
+          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2165,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>/challenge-categories</t>
+          <t>/challenges/{challenge_id}</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>챌린지 카테고리 목록</t>
+          <t>챌린지 상세(v5: 근거출처 배지 제거됨)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2169,7 +2180,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>category_code, category_name, catalog_status(mvp/review/backlog — v8: 아침식사=review, 체중관리=backlog)</t>
+          <t>description (evidence_sources는 식단분석 전용으로 이동)</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2197,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>/challenges</t>
+          <t>/challenges/{challenge_id}/levels</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>챌린지 목록(카테고리 필터)</t>
+          <t>난이도별 목표 조회(상/중/하)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2201,29 +2212,29 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>challenge_code, mission_role_type(fixed/selectable/replacement), proof_type</t>
+          <t>difficulty(low/medium/high), weekly_target, target_config</t>
         </is>
       </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그</t>
+          <t>챌린지 추천</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}</t>
+          <t>/challenge-recommendations</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>챌린지 상세(v5: 근거출처 배지 제거됨)</t>
+          <t>추천 배치 생성(설문+예측 기반)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2233,14 +2244,14 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>description (evidence_sources는 식단분석 전용으로 이동)</t>
+          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
         </is>
       </c>
     </row>
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>챌린지 카탈로그</t>
+          <t>챌린지 추천</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2250,12 +2261,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>/challenges/{challenge_id}/levels</t>
+          <t>/challenge-recommendations/{batch_id}</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>난이도별 목표 조회(상/중/하)</t>
+          <t>추천 후보+이유 조회</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2265,7 +2276,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>difficulty(low/medium/high), weekly_target, target_config</t>
+          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
         </is>
       </c>
     </row>
@@ -2282,12 +2293,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations</t>
+          <t>/challenge-recommendations/{batch_id}/view</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>추천 배치 생성(설문+예측 기반)</t>
+          <t>추천 결과 열람 처리</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2297,29 +2308,29 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>survey_instance_id, prediction_id → recommendation_batch_id</t>
+          <t>viewed_at 기록</t>
         </is>
       </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>챌린지 추천</t>
+          <t>챌린지 사이클·수행</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}</t>
+          <t>/challenge-cycles</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>추천 후보+이유 조회</t>
+          <t>4주 사이클 시작</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2329,29 +2340,29 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>categories[], candidates[](proposed_role, proposed_difficulty), reasons[]</t>
+          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
         </is>
       </c>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>챌린지 추천</t>
+          <t>챌린지 사이클·수행</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>/challenge-recommendations/{batch_id}/view</t>
+          <t>/challenge-cycles/active</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>추천 결과 열람 처리</t>
+          <t>진행중 사이클 조회</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2361,7 +2372,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>viewed_at 기록</t>
+          <t>started_on, ended_on, cycle_challenges[]</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2389,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles</t>
+          <t>/challenge-cycles/{cycle_id}/stop</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>4주 사이클 시작</t>
+          <t>사이클 중단</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2393,7 +2404,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>recommendation_batch_id, cycle_challenges[](challenge_id, challenge_level_id) → cycle_id</t>
+          <t>stopped_reason_code, stopped_note</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2421,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/active</t>
+          <t>/challenge-cycles/{cycle_id}/weeks</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>진행중 사이클 조회</t>
+          <t>주차별 목표·달성 현황</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2425,7 +2436,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>started_on, ended_on, cycle_challenges[]</t>
+          <t>week_number, target_count, achieved_count</t>
         </is>
       </c>
     </row>
@@ -2442,12 +2453,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/stop</t>
+          <t>/cycle-challenges/{id}/logs</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>사이클 중단</t>
+          <t>일일 수행 기록</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2457,7 +2468,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>stopped_reason_code, stopped_note</t>
+          <t>log_date, status, quantity</t>
         </is>
       </c>
     </row>
@@ -2469,17 +2480,17 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>/challenge-cycles/{cycle_id}/weeks</t>
+          <t>/challenge-logs/{log_id}/proofs</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>주차별 목표·달성 현황</t>
+          <t>인증자료 첨부</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2489,14 +2500,14 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>week_number, target_count, achieved_count</t>
+          <t>proof_type, file_job_id, proof_data</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>식단 분석</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -2506,12 +2517,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>/cycle-challenges/{id}/logs</t>
+          <t>/meal-analyses</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>일일 수행 기록</t>
+          <t>식단 사진 분석 요청</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2521,29 +2532,29 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>log_date, status, quantity</t>
+          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
         </is>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>챌린지 사이클·수행</t>
+          <t>식단 분석</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>/challenge-logs/{log_id}/proofs</t>
+          <t>/meal-analyses/{id}</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>인증자료 첨부</t>
+          <t>분석 결과 조회(나트륨 점수)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2553,7 +2564,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>proof_type, file_job_id, proof_data</t>
+          <t>sodium_score, meal_analysis_foods[]</t>
         </is>
       </c>
     </row>
@@ -2565,17 +2576,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses</t>
+          <t>/food-items/search</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>식단 사진 분석 요청</t>
+          <t>음식명 검색(수동 등록용)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2585,14 +2596,14 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>challenge_log_id, file_job_id → meal_analysis_id, analysis_status</t>
+          <t>food_name, sodium_mg, evidence_source_id</t>
         </is>
       </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>식단 분석</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -2602,12 +2613,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>/meal-analyses/{id}</t>
+          <t>/users/me/notification-preferences</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>분석 결과 조회(나트륨 점수)</t>
+          <t>알림 설정 조회</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2617,29 +2628,29 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>sodium_score, meal_analysis_foods[]</t>
+          <t>push_enabled, morning_time, timezone</t>
         </is>
       </c>
     </row>
     <row r="68" ht="32" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>식단 분석</t>
+          <t>알림</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>/food-items/search</t>
+          <t>/users/me/notification-preferences</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>음식명 검색(수동 등록용)</t>
+          <t>알림 설정 변경</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2649,7 +2660,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>food_name, sodium_mg, evidence_source_id</t>
+          <t>push_enabled, morning_time</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2672,17 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notification-preferences</t>
+          <t>/users/me/push-devices</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 조회</t>
+          <t>푸시 토큰 등록</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2681,7 +2692,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time, timezone</t>
+          <t>endpoint, public_key, auth_key</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2704,17 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notification-preferences</t>
+          <t>/users/me/push-devices/{id}</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>알림 설정 변경</t>
+          <t>푸시 토큰 등록 해제</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2713,7 +2724,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>push_enabled, morning_time</t>
+          <t>revoked_at 기록</t>
         </is>
       </c>
     </row>
@@ -2725,17 +2736,17 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices</t>
+          <t>/users/me/notifications</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록</t>
+          <t>발송 내역 조회</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2745,29 +2756,29 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>endpoint, public_key, auth_key</t>
+          <t>notification_deliveries[](status, sent_at)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>피드백</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>/users/me/push-devices/{id}</t>
+          <t>/feedbacks</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>푸시 토큰 등록 해제</t>
+          <t>피드백 등록(예측·추천·사이클 대상)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2777,14 +2788,14 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>revoked_at 기록</t>
+          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
         </is>
       </c>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>알림</t>
+          <t>피드백</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -2794,12 +2805,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>/users/me/notifications</t>
+          <t>/users/me/feedbacks</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>발송 내역 조회</t>
+          <t>내가 남긴 피드백 목록</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2809,7 +2820,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>notification_deliveries[](status, sent_at)</t>
+          <t>feedback_type, rating, created_at</t>
         </is>
       </c>
     </row>
@@ -2821,27 +2832,27 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>/feedbacks</t>
+          <t>/admin/feedback-reports [POST-MVP]</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>피드백 등록(예측·추천·사이클 대상)</t>
+          <t>피드백 분석 리포트 조회</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>관리자</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>prediction_id/recommendation_batch_id/cycle_id, rating, comment</t>
+          <t>period_start, period_end, result_json</t>
         </is>
       </c>
     </row>
@@ -2858,89 +2869,27 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>/users/me/feedbacks</t>
+          <t>/admin/feedback-reports/{id}/actions [POST-MVP]</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>내가 남긴 피드백 목록</t>
+          <t>개선 조치 이력 조회</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>필요</t>
+          <t>관리자</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>feedback_type, rating, created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>/admin/feedback-reports [POST-MVP]</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>피드백 분석 리포트 조회</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>period_start, period_end, result_json</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>피드백</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>/admin/feedback-reports/{id}/actions [POST-MVP]</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>개선 조치 이력 조회</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
           <t>feature_area, proposed_action, status</t>
         </is>
       </c>
     </row>
+    <row r="76" ht="32" customHeight="1"/>
+    <row r="77" ht="32" customHeight="1"/>
   </sheetData>
   <autoFilter ref="A1:F77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3244,7 +3193,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>POST로 job_id 즉시반환 → GET .../{job_id}로 상태(pending/processing/succeeded/failed) 폴링</t>
+          <t>POST로 job_id 즉시반환 → GET .../{job_id}로 상태(pending/processing/succeeded/failed) 폴링 [확인 요청: 백엔드] 예측(/predictions/jobs)은 지금 즉시 계산해 201로 결과를 돌려준다(REQ-PRED-002).</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3259,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>나트륨 5문항 합산 0~10점 → 하(0~3,≤2088mg)/중(4~6)/상(7~10,&gt;3363mg) 3등급 변환(REQ-PRED-008, KNHANES 삼분위수 기준). 이 점수의 최종 용도는 담당자 확인 필요(모델B 실제 피처 12개엔 이 합산점수 없음).</t>
+          <t>[v8.1 수정] 나트륨 지수(Lee 등 2022, 11문항: 짠맛 습관 1 + 식행동 10)와 성별·연령대·BMI로 추정 나트륨(mg/일)·지수·등급을 계산한다(REQ-PRED-008). 모델 입력이 아니라 나트륨·외식 미션 대상 판정에 쓴다. 19~69세이고 고혈압·당뇨가 없을 때만 계산한다.</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3271,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>수동 재예측(request_type=manual)은 사이클당 7일 1회 제한, 초과시 429. 모델A 원시확률 노출 금지, 모델B는 '현재 유사도'로만 표현. 위험판정은 입력혈압규칙(HE_HP)기준.</t>
+          <t>수동 재예측(request_type=manual)은 사이클당 7일 1회 제한, 초과시 429. [확인 요청: 백엔드] 이 제한은 코드에서 확인되지 않음. [v8.1 수정] 모델 A 확률은 한국인 보정값을 "생활습관 관리용 참고 신호"로 % 표시하고 범주는 양호·주의·높음(2%·9%). 모델 B는 숫자 없이 similarity_level 3단계로만 표시. 입력 혈압 판정은 모델과 별개 규칙.</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3283,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>모델A(Framingham,CHD,32~70세,피처9개,AUC0.701)·모델B(KNHANES,경계군유사도,19세+,피처12개,AUC0.745) 둘다 운영중. 두 모델 확률 합산·평균 금지(REQ-PRED-006). [v8 해결] 모델B 반대방향 요인(흡연·외식·운동) 문제는 factor_challenge_links 테이블로 요인별 큐레이션(linked/pending_decision/not_linked)하여 해결. 대체 미션은 모델B가 아닌 모델A의 SHAP상위5 요인 중 linked인 것만 채택.</t>
+          <t>[v8.1 수정] 모델 A v0.2.0(Framingham 계수 + 한국인 성별 절편 보정, 관상동맥질환 10년, 32~70세, 피처 9개, 테스트 AUC 0.701)·모델 B v0.2.0(국민건강영양조사 2022~2024, 혈압 제외 피처 9개, 19세 이상, 테스트 AUC 0.744) 둘 다 운영. 두 모델 확률 합산·평균 금지(REQ-PRED-006). 모델 B 반대 방향 요인(현재·과거 흡연)은 화면 요인 목록에서 뺀다(REQ-PRED-003). 요인은 결과 설명용이며 챌린지 추천·대체에는 쓰지 않는다(factor_challenge_links 삭제).</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3307,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>고정 2(흡연·음주)+선택 1=총 3개 확정(REQ-CHAL-003). 비흡연·비음주자는 modifiable=true이고 risk 기여도가 가장 큰 요인의 미션으로 대체, 그중 나트륨이 후보 1순위(REQ-CHAL-008). 지난 날짜 로그 수정은 403(REQ-CHAL-005). 음주는 남2/여1잔 초과시 경고+실패 처리(REQ-CHAL-010).</t>
+          <t>고정 2(흡연·음주)+선택 1=총 3개 확정(REQ-CHAL-003). [v8.1 수정] 고정 칸에 해당하지 않으면 나트륨 → 신체 활동 → 외식·배달 → 아침 식사 순서로 조건이 맞는 미션으로 대체한다. 모델 기여도는 쓰지 않는다(REQ-CHAL-008 v2.0). 지난 날짜 로그 수정은 403(REQ-CHAL-005). 음주는 남2/여1잔 초과시 경고+실패 처리(REQ-CHAL-010).</t>
         </is>
       </c>
     </row>
@@ -3395,6 +3344,510 @@
       <c r="B11" s="3" t="inlineStr">
         <is>
           <t>[v5] service_health_checks 테이블 삭제 — GET /admin/health는 저장 없이 실시간으로 DB·큐 상태를 점검해 응답. api_request_audits는 POST-MVP, analytics_events·security_audit_logs만 이번 스프린트에서 적재.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>위치</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>수정 전</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>수정 후</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>수정자</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>이용 적합성 (3행)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>/eligibility/assessments POST·GET latest·acknowledge-emergency</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>PUT·GET /users/me/eligibility (응급 확인은 PUT의 emergency_acknowledged로 통합, acknowledge-emergency 행 삭제)</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>구현 기준</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>POST /predictions/jobs</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>비동기 202, request_type(auto/manual)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>즉시 계산 201, survey_instance_id·request_type(initial/interim/full/manual), 결과 형식</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>구현 기준</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>반영 (비동기 여부는 확인 요청: 백엔드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>GET /predictions/jobs/{job_id}</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>작업 상태 조회(폴링)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>그대로 두고 확인 요청 표시</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>구현에 없음, REQ-PRED-002 결정 대기</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>확인 요청: 백엔드</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>GET /predictions/{prediction_id}</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>model_code, risk_level, score, vascular_age 등</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>/predictions/{prediction_job_id}, model_a·model_b 필드 전체(probability·percentile·similarity_level·skip_reason 등)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>모델 A v0.2.0, 구현 기준</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>GET /predictions/latest, GET /predictions</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>model_code별 배열, score·vascular_age</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>실제 응답 형식</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>구현 기준</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>GET /predictions/{prediction_id}/disclosures</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>POST-MVP + 필요한 이유</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>지금은 disclaimer·화면 고정 문구</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>신규 4행</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>GET /reassessments/latest, POST /predict(임시), GET /challenges/cycles/{cycle_id}/review·/challenges/program/review의 모델 부분</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>구현 기준</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>반영 (리뷰 응답의 모델 외 필드는 챌린지 담당)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>모델 관리 /admin/models·versions·activate</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>POST-MVP + 필요해지는 조건</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>지금은 모델 JSON·git</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>모델 관리 feature-contracts, feature-weights</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>삭제 예정</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>NFR-FEED-002 v2.3, 계약은 모델 JSON</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>feature-weights는 확인 요청: 챌린지 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>모델 관리 training-datasets·experiments·metrics, factor-challenge-links 2개</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>실험 기록은 metrics JSON, 요인은 추천에 안 씀(v2.0)</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>도메인별 비고: 설문·예측 실행·결과·모델 관리·챌린지 사이클·수행</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>나트륨 5문항, 원시확률 노출 금지, 모델 B 12개 피처, 기여도로 대체</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>나트륨 지수 11문항, 확률 참고 신호·양호·주의·높음, v0.2.0 피처 9개, 순서대로 대체</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>모델 A·B v0.2.0, 요구사항 v2.3</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>반영 (수동 재예측 7일 제한은 확인 요청: 백엔드)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>공통 규칙: 비동기 작업 패턴</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>POST 후 폴링</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>확인 요청 표시 추가</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>예측은 즉시 계산</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>모델링 담당</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>확인 요청: 백엔드</t>
         </is>
       </c>
     </row>

--- a/docs/api-spec/PAEON_API_명세서.xlsx
+++ b/docs/api-spec/PAEON_API_명세서.xlsx
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>모델링 담당</t>
+          <t>김혜성</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
